--- a/AAII_Financials/Quarterly/BABB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>BABB</t>
   </si>
@@ -656,172 +656,175 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E7" s="2">
         <v>45169</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45077</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44985</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44895</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44804</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44712</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44620</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44530</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44439</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44347</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44255</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44165</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44074</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43982</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43890</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43799</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43708</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43616</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43524</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43434</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43343</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43251</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43159</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43069</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42978</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42886</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42794</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42704</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E8" s="3">
         <v>900</v>
       </c>
       <c r="F8" s="3">
+        <v>900</v>
+      </c>
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>700</v>
-      </c>
-      <c r="K8" s="3">
-        <v>800</v>
       </c>
       <c r="L8" s="3">
         <v>800</v>
       </c>
       <c r="M8" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="N8" s="3">
         <v>700</v>
@@ -830,16 +833,16 @@
         <v>700</v>
       </c>
       <c r="P8" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q8" s="3">
         <v>600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>700</v>
-      </c>
-      <c r="S8" s="3">
-        <v>800</v>
       </c>
       <c r="T8" s="3">
         <v>800</v>
@@ -848,10 +851,10 @@
         <v>800</v>
       </c>
       <c r="V8" s="3">
+        <v>800</v>
+      </c>
+      <c r="W8" s="3">
         <v>700</v>
-      </c>
-      <c r="W8" s="3">
-        <v>600</v>
       </c>
       <c r="X8" s="3">
         <v>600</v>
@@ -860,10 +863,10 @@
         <v>600</v>
       </c>
       <c r="Z8" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA8" s="3">
         <v>500</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>600</v>
       </c>
       <c r="AB8" s="3">
         <v>600</v>
@@ -872,16 +875,19 @@
         <v>600</v>
       </c>
       <c r="AD8" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE8" s="3">
         <v>500</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>600</v>
       </c>
       <c r="AF8" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,8 +978,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1296,8 +1315,8 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1318,11 +1337,11 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1338,8 +1357,8 @@
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1374,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,13 +1522,14 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E17" s="3">
         <v>700</v>
@@ -1521,37 +1547,37 @@
         <v>700</v>
       </c>
       <c r="J17" s="3">
+        <v>700</v>
+      </c>
+      <c r="K17" s="3">
         <v>600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>700</v>
-      </c>
-      <c r="L17" s="3">
-        <v>600</v>
       </c>
       <c r="M17" s="3">
         <v>600</v>
       </c>
       <c r="N17" s="3">
+        <v>600</v>
+      </c>
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>700</v>
-      </c>
-      <c r="T17" s="3">
-        <v>600</v>
       </c>
       <c r="U17" s="3">
         <v>600</v>
@@ -1560,10 +1586,10 @@
         <v>600</v>
       </c>
       <c r="W17" s="3">
+        <v>600</v>
+      </c>
+      <c r="X17" s="3">
         <v>500</v>
-      </c>
-      <c r="X17" s="3">
-        <v>400</v>
       </c>
       <c r="Y17" s="3">
         <v>400</v>
@@ -1578,19 +1604,22 @@
         <v>400</v>
       </c>
       <c r="AC17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD17" s="3">
         <v>500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1601,16 +1630,16 @@
         <v>200</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J18" s="3">
         <v>100</v>
@@ -1619,70 +1648,73 @@
         <v>100</v>
       </c>
       <c r="L18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N18" s="3">
+        <v>100</v>
+      </c>
+      <c r="O18" s="3">
         <v>300</v>
       </c>
-      <c r="O18" s="3">
-        <v>100</v>
-      </c>
       <c r="P18" s="3">
         <v>100</v>
       </c>
       <c r="Q18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3">
         <v>100</v>
       </c>
       <c r="T18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U18" s="3">
         <v>200</v>
       </c>
       <c r="V18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W18" s="3">
         <v>100</v>
       </c>
       <c r="X18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y18" s="3">
         <v>200</v>
       </c>
       <c r="Z18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB18" s="3">
         <v>200</v>
       </c>
       <c r="AC18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD18" s="3">
         <v>100</v>
       </c>
       <c r="AE18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF18" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,16 +1747,17 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1807,8 +1840,11 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1819,16 +1855,16 @@
         <v>200</v>
       </c>
       <c r="F21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H21" s="3">
         <v>200</v>
       </c>
       <c r="I21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J21" s="3">
         <v>100</v>
@@ -1837,34 +1873,34 @@
         <v>100</v>
       </c>
       <c r="L21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N21" s="3">
+        <v>100</v>
+      </c>
+      <c r="O21" s="3">
         <v>400</v>
       </c>
-      <c r="O21" s="3">
-        <v>100</v>
-      </c>
       <c r="P21" s="3">
         <v>100</v>
       </c>
       <c r="Q21" s="3">
+        <v>100</v>
+      </c>
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3">
-        <v>100</v>
-      </c>
       <c r="S21" s="3">
         <v>100</v>
       </c>
       <c r="T21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V21" s="3">
         <v>100</v>
@@ -1873,13 +1909,13 @@
         <v>100</v>
       </c>
       <c r="X21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y21" s="3">
         <v>200</v>
       </c>
       <c r="Z21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA21" s="3">
         <v>100</v>
@@ -1897,10 +1933,13 @@
         <v>100</v>
       </c>
       <c r="AF21" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1967,14 +2006,14 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1991,8 +2030,11 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2003,16 +2045,16 @@
         <v>200</v>
       </c>
       <c r="F23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G23" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3">
         <v>200</v>
       </c>
       <c r="I23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J23" s="3">
         <v>100</v>
@@ -2021,34 +2063,34 @@
         <v>100</v>
       </c>
       <c r="L23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N23" s="3">
+        <v>100</v>
+      </c>
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="O23" s="3">
-        <v>100</v>
-      </c>
       <c r="P23" s="3">
         <v>100</v>
       </c>
       <c r="Q23" s="3">
+        <v>100</v>
+      </c>
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
-        <v>100</v>
-      </c>
       <c r="S23" s="3">
         <v>100</v>
       </c>
       <c r="T23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V23" s="3">
         <v>100</v>
@@ -2057,13 +2099,13 @@
         <v>100</v>
       </c>
       <c r="X23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y23" s="3">
         <v>200</v>
       </c>
       <c r="Z23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA23" s="3">
         <v>100</v>
@@ -2081,10 +2123,13 @@
         <v>100</v>
       </c>
       <c r="AF23" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2095,16 +2140,16 @@
         <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -2113,20 +2158,20 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -2146,11 +2191,11 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
@@ -2175,8 +2220,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,28 +2315,31 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J26" s="3">
         <v>100</v>
@@ -2303,22 +2354,22 @@
         <v>100</v>
       </c>
       <c r="N26" s="3">
+        <v>100</v>
+      </c>
+      <c r="O26" s="3">
         <v>300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-100</v>
       </c>
-      <c r="P26" s="3">
-        <v>100</v>
-      </c>
       <c r="Q26" s="3">
+        <v>100</v>
+      </c>
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T26" s="3">
         <v>100</v>
@@ -2330,16 +2381,16 @@
         <v>100</v>
       </c>
       <c r="W26" s="3">
+        <v>100</v>
+      </c>
+      <c r="X26" s="3">
         <v>300</v>
       </c>
-      <c r="X26" s="3">
-        <v>200</v>
-      </c>
       <c r="Y26" s="3">
         <v>200</v>
       </c>
       <c r="Z26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA26" s="3">
         <v>100</v>
@@ -2357,30 +2408,33 @@
         <v>100</v>
       </c>
       <c r="AF26" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J27" s="3">
         <v>100</v>
@@ -2395,22 +2449,22 @@
         <v>100</v>
       </c>
       <c r="N27" s="3">
+        <v>100</v>
+      </c>
+      <c r="O27" s="3">
         <v>300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="P27" s="3">
-        <v>100</v>
-      </c>
       <c r="Q27" s="3">
+        <v>100</v>
+      </c>
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T27" s="3">
         <v>100</v>
@@ -2422,16 +2476,16 @@
         <v>100</v>
       </c>
       <c r="W27" s="3">
+        <v>100</v>
+      </c>
+      <c r="X27" s="3">
         <v>300</v>
       </c>
-      <c r="X27" s="3">
-        <v>200</v>
-      </c>
       <c r="Y27" s="3">
         <v>200</v>
       </c>
       <c r="Z27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA27" s="3">
         <v>100</v>
@@ -2449,10 +2503,13 @@
         <v>100</v>
       </c>
       <c r="AF27" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2587,8 +2647,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
@@ -2605,12 +2665,12 @@
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
         <v>-200</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2626,8 +2686,8 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,17 +2885,20 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
@@ -2911,28 +2980,31 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J33" s="3">
         <v>100</v>
@@ -2947,22 +3019,22 @@
         <v>100</v>
       </c>
       <c r="N33" s="3">
+        <v>100</v>
+      </c>
+      <c r="O33" s="3">
         <v>300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="P33" s="3">
-        <v>100</v>
-      </c>
       <c r="Q33" s="3">
+        <v>100</v>
+      </c>
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T33" s="3">
         <v>100</v>
@@ -2977,13 +3049,13 @@
         <v>100</v>
       </c>
       <c r="X33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y33" s="3">
         <v>200</v>
       </c>
       <c r="Z33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA33" s="3">
         <v>100</v>
@@ -3001,10 +3073,13 @@
         <v>100</v>
       </c>
       <c r="AF33" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,28 +3170,31 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J35" s="3">
         <v>100</v>
@@ -3131,22 +3209,22 @@
         <v>100</v>
       </c>
       <c r="N35" s="3">
+        <v>100</v>
+      </c>
+      <c r="O35" s="3">
         <v>300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="P35" s="3">
-        <v>100</v>
-      </c>
       <c r="Q35" s="3">
+        <v>100</v>
+      </c>
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T35" s="3">
         <v>100</v>
@@ -3161,13 +3239,13 @@
         <v>100</v>
       </c>
       <c r="X35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y35" s="3">
         <v>200</v>
       </c>
       <c r="Z35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA35" s="3">
         <v>100</v>
@@ -3185,107 +3263,113 @@
         <v>100</v>
       </c>
       <c r="AF35" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E38" s="2">
         <v>45169</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45077</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44985</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44895</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44804</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44712</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44620</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44530</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44439</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44347</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44255</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44165</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44074</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43982</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43890</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43799</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43708</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43616</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43524</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43434</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43343</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43251</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43159</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43069</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42978</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42886</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42794</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42704</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,25 +3437,26 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="E41" s="3">
         <v>1700</v>
       </c>
       <c r="F41" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G41" s="3">
         <v>1600</v>
       </c>
       <c r="H41" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="I41" s="3">
         <v>1500</v>
@@ -3385,28 +3471,28 @@
         <v>1500</v>
       </c>
       <c r="M41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N41" s="3">
         <v>1400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1100</v>
-      </c>
-      <c r="T41" s="3">
-        <v>1000</v>
       </c>
       <c r="U41" s="3">
         <v>1000</v>
@@ -3415,37 +3501,40 @@
         <v>1000</v>
       </c>
       <c r="W41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X41" s="3">
         <v>1100</v>
-      </c>
-      <c r="X41" s="3">
-        <v>900</v>
       </c>
       <c r="Y41" s="3">
         <v>900</v>
       </c>
       <c r="Z41" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="AA41" s="3">
         <v>800</v>
       </c>
       <c r="AB41" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC41" s="3">
         <v>700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,8 +3625,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3581,10 +3673,10 @@
         <v>100</v>
       </c>
       <c r="Q43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S43" s="3">
         <v>100</v>
@@ -3628,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3687,11 +3782,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
@@ -3720,31 +3815,34 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
       </c>
       <c r="F45" s="3">
+        <v>400</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>700</v>
       </c>
       <c r="K45" s="3">
         <v>700</v>
@@ -3753,7 +3851,7 @@
         <v>700</v>
       </c>
       <c r="M45" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="N45" s="3">
         <v>500</v>
@@ -3762,13 +3860,13 @@
         <v>500</v>
       </c>
       <c r="P45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
-      </c>
-      <c r="R45" s="3">
-        <v>500</v>
       </c>
       <c r="S45" s="3">
         <v>500</v>
@@ -3786,13 +3884,13 @@
         <v>500</v>
       </c>
       <c r="X45" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="Y45" s="3">
         <v>700</v>
       </c>
       <c r="Z45" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AA45" s="3">
         <v>800</v>
@@ -3801,7 +3899,7 @@
         <v>800</v>
       </c>
       <c r="AC45" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AD45" s="3">
         <v>700</v>
@@ -3812,13 +3910,16 @@
       <c r="AF45" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="E46" s="3">
         <v>2200</v>
@@ -3830,82 +3931,85 @@
         <v>2200</v>
       </c>
       <c r="H46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I46" s="3">
         <v>2600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2400</v>
-      </c>
-      <c r="J46" s="3">
-        <v>2300</v>
       </c>
       <c r="K46" s="3">
         <v>2300</v>
       </c>
       <c r="L46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M46" s="3">
         <v>2200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1700</v>
-      </c>
-      <c r="T46" s="3">
-        <v>1600</v>
       </c>
       <c r="U46" s="3">
         <v>1600</v>
       </c>
       <c r="V46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W46" s="3">
         <v>1500</v>
-      </c>
-      <c r="W46" s="3">
-        <v>1700</v>
       </c>
       <c r="X46" s="3">
         <v>1700</v>
       </c>
       <c r="Y46" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="Z46" s="3">
         <v>1600</v>
       </c>
       <c r="AA46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AB46" s="3">
         <v>1700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1600</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>1500</v>
       </c>
       <c r="AD46" s="3">
         <v>1500</v>
       </c>
       <c r="AE46" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF46" s="3">
         <v>1700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3924,8 +4028,8 @@
       <c r="H47" s="3">
         <v>0</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
+      <c r="I47" s="3">
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -3942,8 +4046,8 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3996,13 +4100,16 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
         <v>100</v>
@@ -4014,7 +4121,7 @@
         <v>100</v>
       </c>
       <c r="H48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I48" s="3">
         <v>200</v>
@@ -4029,7 +4136,7 @@
         <v>200</v>
       </c>
       <c r="M48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N48" s="3">
         <v>300</v>
@@ -4044,7 +4151,7 @@
         <v>300</v>
       </c>
       <c r="R48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S48" s="3">
         <v>400</v>
@@ -4056,13 +4163,13 @@
         <v>400</v>
       </c>
       <c r="V48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W48" s="3">
         <v>500</v>
       </c>
       <c r="X48" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -4088,8 +4195,11 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3">
         <v>2000</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,16 +4480,19 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>5</v>
@@ -4384,14 +4503,14 @@
       <c r="H52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>5</v>
@@ -4402,11 +4521,11 @@
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>200</v>
@@ -4456,8 +4575,11 @@
       <c r="AF52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,8 +4670,11 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4566,10 +4691,10 @@
         <v>4300</v>
       </c>
       <c r="H54" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I54" s="3">
         <v>4800</v>
-      </c>
-      <c r="I54" s="3">
-        <v>4500</v>
       </c>
       <c r="J54" s="3">
         <v>4500</v>
@@ -4578,28 +4703,28 @@
         <v>4500</v>
       </c>
       <c r="L54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="M54" s="3">
         <v>4400</v>
-      </c>
-      <c r="M54" s="3">
-        <v>4200</v>
       </c>
       <c r="N54" s="3">
         <v>4200</v>
       </c>
       <c r="O54" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="P54" s="3">
         <v>4100</v>
       </c>
       <c r="Q54" s="3">
+        <v>4100</v>
+      </c>
+      <c r="R54" s="3">
         <v>3900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4000</v>
-      </c>
-      <c r="S54" s="3">
-        <v>4200</v>
       </c>
       <c r="T54" s="3">
         <v>4200</v>
@@ -4611,37 +4736,40 @@
         <v>4200</v>
       </c>
       <c r="W54" s="3">
+        <v>4200</v>
+      </c>
+      <c r="X54" s="3">
         <v>4400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3900</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>3800</v>
       </c>
       <c r="Z54" s="3">
         <v>3800</v>
       </c>
       <c r="AA54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AB54" s="3">
         <v>3900</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>3800</v>
       </c>
       <c r="AC54" s="3">
         <v>3800</v>
       </c>
       <c r="AD54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AE54" s="3">
         <v>3700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4837,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4789,19 +4919,22 @@
         <v>0</v>
       </c>
       <c r="AC57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD57" s="3">
         <v>100</v>
       </c>
       <c r="AE57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4839,13 +4972,13 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
+        <v>200</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>100</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>5</v>
@@ -4862,8 +4995,8 @@
       <c r="V58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4883,76 +5016,79 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E59" s="3">
         <v>800</v>
       </c>
       <c r="F59" s="3">
+        <v>800</v>
+      </c>
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1100</v>
       </c>
       <c r="K59" s="3">
         <v>1100</v>
       </c>
       <c r="L59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M59" s="3">
         <v>1000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>900</v>
       </c>
       <c r="N59" s="3">
         <v>900</v>
       </c>
       <c r="O59" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="P59" s="3">
         <v>800</v>
       </c>
       <c r="Q59" s="3">
+        <v>800</v>
+      </c>
+      <c r="R59" s="3">
         <v>700</v>
-      </c>
-      <c r="R59" s="3">
-        <v>900</v>
       </c>
       <c r="S59" s="3">
         <v>900</v>
       </c>
       <c r="T59" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="U59" s="3">
         <v>800</v>
       </c>
       <c r="V59" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="W59" s="3">
         <v>900</v>
@@ -4964,7 +5100,7 @@
         <v>900</v>
       </c>
       <c r="Z59" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AA59" s="3">
         <v>1000</v>
@@ -4979,69 +5115,72 @@
         <v>1000</v>
       </c>
       <c r="AE59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF59" s="3">
         <v>1100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>600</v>
+      </c>
+      <c r="E60" s="3">
         <v>800</v>
-      </c>
-      <c r="E60" s="3">
-        <v>900</v>
       </c>
       <c r="F60" s="3">
         <v>900</v>
       </c>
       <c r="G60" s="3">
+        <v>900</v>
+      </c>
+      <c r="H60" s="3">
         <v>800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1200</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1100</v>
       </c>
       <c r="K60" s="3">
         <v>1100</v>
       </c>
       <c r="L60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M60" s="3">
         <v>1000</v>
-      </c>
-      <c r="M60" s="3">
-        <v>900</v>
       </c>
       <c r="N60" s="3">
         <v>900</v>
       </c>
       <c r="O60" s="3">
+        <v>900</v>
+      </c>
+      <c r="P60" s="3">
         <v>1100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>700</v>
-      </c>
-      <c r="R60" s="3">
-        <v>900</v>
       </c>
       <c r="S60" s="3">
         <v>900</v>
       </c>
       <c r="T60" s="3">
+        <v>900</v>
+      </c>
+      <c r="U60" s="3">
         <v>800</v>
-      </c>
-      <c r="U60" s="3">
-        <v>900</v>
       </c>
       <c r="V60" s="3">
         <v>900</v>
@@ -5056,7 +5195,7 @@
         <v>900</v>
       </c>
       <c r="Z60" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AA60" s="3">
         <v>1000</v>
@@ -5068,16 +5207,19 @@
         <v>1000</v>
       </c>
       <c r="AD60" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="AE60" s="3">
         <v>1100</v>
       </c>
       <c r="AF60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG60" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5118,13 +5260,13 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -5168,13 +5310,16 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E62" s="3">
         <v>400</v>
@@ -5198,10 +5343,10 @@
         <v>400</v>
       </c>
       <c r="L62" s="3">
+        <v>400</v>
+      </c>
+      <c r="M62" s="3">
         <v>500</v>
-      </c>
-      <c r="M62" s="3">
-        <v>400</v>
       </c>
       <c r="N62" s="3">
         <v>400</v>
@@ -5222,7 +5367,7 @@
         <v>400</v>
       </c>
       <c r="T62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U62" s="3">
         <v>500</v>
@@ -5231,11 +5376,11 @@
         <v>500</v>
       </c>
       <c r="W62" s="3">
+        <v>500</v>
+      </c>
+      <c r="X62" s="3">
         <v>400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5251,8 +5396,8 @@
       <c r="AC62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,52 +5690,55 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1200</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1300</v>
       </c>
       <c r="F66" s="3">
         <v>1300</v>
       </c>
       <c r="G66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H66" s="3">
         <v>1200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1700</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1600</v>
       </c>
       <c r="J66" s="3">
         <v>1600</v>
       </c>
       <c r="K66" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="L66" s="3">
         <v>1500</v>
       </c>
       <c r="M66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N66" s="3">
         <v>1400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>1300</v>
       </c>
       <c r="R66" s="3">
         <v>1300</v>
@@ -5593,7 +5750,7 @@
         <v>1300</v>
       </c>
       <c r="U66" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="V66" s="3">
         <v>1400</v>
@@ -5602,13 +5759,13 @@
         <v>1400</v>
       </c>
       <c r="X66" s="3">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="Y66" s="3">
         <v>900</v>
       </c>
       <c r="Z66" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AA66" s="3">
         <v>1000</v>
@@ -5620,16 +5777,19 @@
         <v>1000</v>
       </c>
       <c r="AD66" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="AE66" s="3">
         <v>1100</v>
       </c>
       <c r="AF66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG66" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,28 +6200,31 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11200</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-11300</v>
       </c>
       <c r="F72" s="3">
         <v>-11300</v>
       </c>
       <c r="G72" s="3">
-        <v>-11200</v>
+        <v>-11300</v>
       </c>
       <c r="H72" s="3">
         <v>-11200</v>
       </c>
       <c r="I72" s="3">
-        <v>-11300</v>
+        <v>-11200</v>
       </c>
       <c r="J72" s="3">
         <v>-11300</v>
@@ -6060,7 +6233,7 @@
         <v>-11300</v>
       </c>
       <c r="L72" s="3">
-        <v>-11400</v>
+        <v>-11300</v>
       </c>
       <c r="M72" s="3">
         <v>-11400</v>
@@ -6069,61 +6242,64 @@
         <v>-11400</v>
       </c>
       <c r="O72" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="P72" s="3">
         <v>-11700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-11700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11500</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-11300</v>
       </c>
       <c r="T72" s="3">
         <v>-11300</v>
       </c>
       <c r="U72" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="V72" s="3">
         <v>-11400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-11500</v>
-      </c>
-      <c r="W72" s="3">
-        <v>-11300</v>
       </c>
       <c r="X72" s="3">
         <v>-11300</v>
       </c>
       <c r="Y72" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11400</v>
-      </c>
-      <c r="AB72" s="3">
-        <v>-11500</v>
       </c>
       <c r="AC72" s="3">
         <v>-11500</v>
       </c>
       <c r="AD72" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="AE72" s="3">
         <v>-11600</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>-11500</v>
       </c>
       <c r="AF72" s="3">
         <v>-11500</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>-11500</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,28 +6580,31 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3100</v>
-      </c>
-      <c r="E76" s="3">
-        <v>3000</v>
       </c>
       <c r="F76" s="3">
         <v>3000</v>
       </c>
       <c r="G76" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H76" s="3">
         <v>3100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>2900</v>
       </c>
       <c r="J76" s="3">
         <v>2900</v>
@@ -6431,25 +6616,25 @@
         <v>2900</v>
       </c>
       <c r="M76" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="N76" s="3">
         <v>2800</v>
       </c>
       <c r="O76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P76" s="3">
         <v>2600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2800</v>
-      </c>
-      <c r="S76" s="3">
-        <v>2900</v>
       </c>
       <c r="T76" s="3">
         <v>2900</v>
@@ -6458,40 +6643,43 @@
         <v>2900</v>
       </c>
       <c r="V76" s="3">
+        <v>2900</v>
+      </c>
+      <c r="W76" s="3">
         <v>2800</v>
-      </c>
-      <c r="W76" s="3">
-        <v>3000</v>
       </c>
       <c r="X76" s="3">
         <v>3000</v>
       </c>
       <c r="Y76" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Z76" s="3">
         <v>2900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2800</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>2700</v>
       </c>
       <c r="AD76" s="3">
         <v>2700</v>
       </c>
       <c r="AE76" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="AF76" s="3">
         <v>2800</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,125 +6770,131 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E80" s="2">
         <v>45169</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45077</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44985</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44895</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44804</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44712</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44620</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44530</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44439</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44347</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44255</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44165</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44074</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43982</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43890</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43799</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43708</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43616</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43524</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43434</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43343</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43251</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43159</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43069</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42978</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42886</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42794</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42704</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J81" s="3">
         <v>100</v>
@@ -6715,22 +6909,22 @@
         <v>100</v>
       </c>
       <c r="N81" s="3">
+        <v>100</v>
+      </c>
+      <c r="O81" s="3">
         <v>300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="P81" s="3">
-        <v>100</v>
-      </c>
       <c r="Q81" s="3">
+        <v>100</v>
+      </c>
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T81" s="3">
         <v>100</v>
@@ -6745,13 +6939,13 @@
         <v>100</v>
       </c>
       <c r="X81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y81" s="3">
         <v>200</v>
       </c>
       <c r="Z81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA81" s="3">
         <v>100</v>
@@ -6769,10 +6963,13 @@
         <v>100</v>
       </c>
       <c r="AF81" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG81" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7095,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7570,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7366,20 +7582,20 @@
         <v>100</v>
       </c>
       <c r="E89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F89" s="3">
         <v>200</v>
       </c>
       <c r="G89" s="3">
+        <v>200</v>
+      </c>
+      <c r="H89" s="3">
         <v>-400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
-        <v>100</v>
-      </c>
       <c r="J89" s="3">
         <v>100</v>
       </c>
@@ -7387,31 +7603,31 @@
         <v>100</v>
       </c>
       <c r="L89" s="3">
+        <v>100</v>
+      </c>
+      <c r="M89" s="3">
         <v>300</v>
       </c>
-      <c r="M89" s="3">
-        <v>200</v>
-      </c>
       <c r="N89" s="3">
         <v>200</v>
       </c>
       <c r="O89" s="3">
+        <v>200</v>
+      </c>
+      <c r="P89" s="3">
         <v>300</v>
       </c>
-      <c r="P89" s="3">
-        <v>100</v>
-      </c>
       <c r="Q89" s="3">
+        <v>100</v>
+      </c>
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
-        <v>100</v>
-      </c>
       <c r="S89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U89" s="3">
         <v>100</v>
@@ -7420,37 +7636,40 @@
         <v>100</v>
       </c>
       <c r="W89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X89" s="3">
         <v>200</v>
       </c>
       <c r="Y89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB89" s="3">
         <v>100</v>
       </c>
       <c r="AC89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD89" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
-        <v>200</v>
-      </c>
       <c r="AF89" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7515,8 +7735,8 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>5</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>5</v>
@@ -7527,8 +7747,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7551,14 +7771,14 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -7569,14 +7789,17 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
+      <c r="AE91" s="3">
+        <v>0</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +7985,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7851,8 +8080,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7924,19 +8157,19 @@
         <v>-100</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-200</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-100</v>
       </c>
       <c r="T96" s="3">
         <v>-100</v>
@@ -7945,10 +8178,10 @@
         <v>-100</v>
       </c>
       <c r="V96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W96" s="3">
         <v>-200</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-100</v>
       </c>
       <c r="X96" s="3">
         <v>-100</v>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8495,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8292,19 +8537,19 @@
         <v>-100</v>
       </c>
       <c r="O100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>200</v>
+      </c>
+      <c r="S100" s="3">
         <v>-200</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-100</v>
       </c>
       <c r="T100" s="3">
         <v>-100</v>
@@ -8313,10 +8558,10 @@
         <v>-100</v>
       </c>
       <c r="V100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W100" s="3">
         <v>-200</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-100</v>
       </c>
       <c r="X100" s="3">
         <v>-100</v>
@@ -8345,8 +8590,11 @@
       <c r="AF100" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,8 +8685,11 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8446,62 +8697,62 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
-        <v>200</v>
-      </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>100</v>
       </c>
       <c r="L102" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M102" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N102" s="3">
         <v>100</v>
       </c>
       <c r="O102" s="3">
+        <v>100</v>
+      </c>
+      <c r="P102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
-        <v>100</v>
-      </c>
       <c r="Q102" s="3">
+        <v>100</v>
+      </c>
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
-        <v>100</v>
-      </c>
       <c r="T102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
-        <v>100</v>
-      </c>
       <c r="X102" s="3">
         <v>100</v>
       </c>
@@ -8509,7 +8760,7 @@
         <v>100</v>
       </c>
       <c r="Z102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
@@ -8518,15 +8769,18 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
-        <v>100</v>
-      </c>
       <c r="AF102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BABB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>BABB</t>
   </si>
@@ -656,178 +656,182 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E7" s="2">
         <v>45260</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45169</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45077</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44985</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44895</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44804</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44712</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44620</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44530</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44439</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44347</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44255</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44165</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44074</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43982</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43890</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43799</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43708</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43616</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43524</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43434</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43343</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43251</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43159</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43069</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42978</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42886</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42794</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42704</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1000</v>
-      </c>
-      <c r="E8" s="3">
-        <v>900</v>
       </c>
       <c r="F8" s="3">
         <v>900</v>
       </c>
       <c r="G8" s="3">
+        <v>900</v>
+      </c>
+      <c r="H8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>700</v>
-      </c>
-      <c r="L8" s="3">
-        <v>800</v>
       </c>
       <c r="M8" s="3">
         <v>800</v>
       </c>
       <c r="N8" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="O8" s="3">
         <v>700</v>
@@ -836,16 +840,16 @@
         <v>700</v>
       </c>
       <c r="Q8" s="3">
+        <v>700</v>
+      </c>
+      <c r="R8" s="3">
         <v>600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>700</v>
-      </c>
-      <c r="T8" s="3">
-        <v>800</v>
       </c>
       <c r="U8" s="3">
         <v>800</v>
@@ -854,10 +858,10 @@
         <v>800</v>
       </c>
       <c r="W8" s="3">
+        <v>800</v>
+      </c>
+      <c r="X8" s="3">
         <v>700</v>
-      </c>
-      <c r="X8" s="3">
-        <v>600</v>
       </c>
       <c r="Y8" s="3">
         <v>600</v>
@@ -866,10 +870,10 @@
         <v>600</v>
       </c>
       <c r="AA8" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB8" s="3">
         <v>500</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>600</v>
       </c>
       <c r="AC8" s="3">
         <v>600</v>
@@ -878,16 +882,19 @@
         <v>600</v>
       </c>
       <c r="AE8" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF8" s="3">
         <v>500</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>600</v>
       </c>
       <c r="AG8" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1318,8 +1338,8 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1340,11 +1360,11 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1360,8 +1380,8 @@
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,16 +1549,17 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>700</v>
+      </c>
+      <c r="E17" s="3">
         <v>800</v>
-      </c>
-      <c r="E17" s="3">
-        <v>700</v>
       </c>
       <c r="F17" s="3">
         <v>700</v>
@@ -1550,37 +1577,37 @@
         <v>700</v>
       </c>
       <c r="K17" s="3">
+        <v>700</v>
+      </c>
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>700</v>
-      </c>
-      <c r="M17" s="3">
-        <v>600</v>
       </c>
       <c r="N17" s="3">
         <v>600</v>
       </c>
       <c r="O17" s="3">
+        <v>600</v>
+      </c>
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>700</v>
-      </c>
-      <c r="U17" s="3">
-        <v>600</v>
       </c>
       <c r="V17" s="3">
         <v>600</v>
@@ -1589,10 +1616,10 @@
         <v>600</v>
       </c>
       <c r="X17" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y17" s="3">
         <v>500</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>400</v>
       </c>
       <c r="Z17" s="3">
         <v>400</v>
@@ -1607,24 +1634,27 @@
         <v>400</v>
       </c>
       <c r="AD17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE17" s="3">
         <v>500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E18" s="3">
         <v>200</v>
@@ -1633,16 +1663,16 @@
         <v>200</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K18" s="3">
         <v>100</v>
@@ -1651,70 +1681,73 @@
         <v>100</v>
       </c>
       <c r="M18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O18" s="3">
+        <v>100</v>
+      </c>
+      <c r="P18" s="3">
         <v>300</v>
       </c>
-      <c r="P18" s="3">
-        <v>100</v>
-      </c>
       <c r="Q18" s="3">
         <v>100</v>
       </c>
       <c r="R18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T18" s="3">
         <v>100</v>
       </c>
       <c r="U18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V18" s="3">
         <v>200</v>
       </c>
       <c r="W18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X18" s="3">
         <v>100</v>
       </c>
       <c r="Y18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z18" s="3">
         <v>200</v>
       </c>
       <c r="AA18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC18" s="3">
         <v>200</v>
       </c>
       <c r="AD18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE18" s="3">
         <v>100</v>
       </c>
       <c r="AF18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG18" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,19 +1781,20 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -1843,13 +1877,16 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3">
         <v>200</v>
@@ -1858,16 +1895,16 @@
         <v>200</v>
       </c>
       <c r="G21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I21" s="3">
         <v>200</v>
       </c>
       <c r="J21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K21" s="3">
         <v>100</v>
@@ -1876,34 +1913,34 @@
         <v>100</v>
       </c>
       <c r="M21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O21" s="3">
+        <v>100</v>
+      </c>
+      <c r="P21" s="3">
         <v>400</v>
       </c>
-      <c r="P21" s="3">
-        <v>100</v>
-      </c>
       <c r="Q21" s="3">
         <v>100</v>
       </c>
       <c r="R21" s="3">
+        <v>100</v>
+      </c>
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
-        <v>100</v>
-      </c>
       <c r="T21" s="3">
         <v>100</v>
       </c>
       <c r="U21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W21" s="3">
         <v>100</v>
@@ -1912,13 +1949,13 @@
         <v>100</v>
       </c>
       <c r="Y21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z21" s="3">
         <v>200</v>
       </c>
       <c r="AA21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB21" s="3">
         <v>100</v>
@@ -1936,10 +1973,13 @@
         <v>100</v>
       </c>
       <c r="AG21" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2009,14 +2049,14 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2033,13 +2073,16 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E23" s="3">
         <v>200</v>
@@ -2048,16 +2091,16 @@
         <v>200</v>
       </c>
       <c r="G23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H23" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
         <v>200</v>
       </c>
       <c r="J23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K23" s="3">
         <v>100</v>
@@ -2066,34 +2109,34 @@
         <v>100</v>
       </c>
       <c r="M23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O23" s="3">
+        <v>100</v>
+      </c>
+      <c r="P23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3">
-        <v>100</v>
-      </c>
       <c r="Q23" s="3">
         <v>100</v>
       </c>
       <c r="R23" s="3">
+        <v>100</v>
+      </c>
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
-        <v>100</v>
-      </c>
       <c r="T23" s="3">
         <v>100</v>
       </c>
       <c r="U23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W23" s="3">
         <v>100</v>
@@ -2102,13 +2145,13 @@
         <v>100</v>
       </c>
       <c r="Y23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z23" s="3">
         <v>200</v>
       </c>
       <c r="AA23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB23" s="3">
         <v>100</v>
@@ -2126,15 +2169,18 @@
         <v>100</v>
       </c>
       <c r="AG23" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
@@ -2143,16 +2189,16 @@
         <v>100</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2161,20 +2207,20 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -2194,11 +2240,11 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
@@ -2223,8 +2269,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,8 +2367,11 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2327,22 +2379,22 @@
         <v>100</v>
       </c>
       <c r="E26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K26" s="3">
         <v>100</v>
@@ -2357,22 +2409,22 @@
         <v>100</v>
       </c>
       <c r="O26" s="3">
+        <v>100</v>
+      </c>
+      <c r="P26" s="3">
         <v>300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
-        <v>100</v>
-      </c>
       <c r="R26" s="3">
+        <v>100</v>
+      </c>
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U26" s="3">
         <v>100</v>
@@ -2384,16 +2436,16 @@
         <v>100</v>
       </c>
       <c r="X26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y26" s="3">
         <v>300</v>
       </c>
-      <c r="Y26" s="3">
-        <v>200</v>
-      </c>
       <c r="Z26" s="3">
         <v>200</v>
       </c>
       <c r="AA26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB26" s="3">
         <v>100</v>
@@ -2411,10 +2463,13 @@
         <v>100</v>
       </c>
       <c r="AG26" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2422,22 +2477,22 @@
         <v>100</v>
       </c>
       <c r="E27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K27" s="3">
         <v>100</v>
@@ -2452,22 +2507,22 @@
         <v>100</v>
       </c>
       <c r="O27" s="3">
+        <v>100</v>
+      </c>
+      <c r="P27" s="3">
         <v>300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
-        <v>100</v>
-      </c>
       <c r="R27" s="3">
+        <v>100</v>
+      </c>
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U27" s="3">
         <v>100</v>
@@ -2479,16 +2534,16 @@
         <v>100</v>
       </c>
       <c r="X27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y27" s="3">
         <v>300</v>
       </c>
-      <c r="Y27" s="3">
-        <v>200</v>
-      </c>
       <c r="Z27" s="3">
         <v>200</v>
       </c>
       <c r="AA27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB27" s="3">
         <v>100</v>
@@ -2506,10 +2561,13 @@
         <v>100</v>
       </c>
       <c r="AG27" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2650,8 +2711,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>5</v>
@@ -2668,12 +2729,12 @@
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-200</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2689,8 +2750,8 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,20 +2955,23 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2983,8 +3053,11 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2992,22 +3065,22 @@
         <v>100</v>
       </c>
       <c r="E33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K33" s="3">
         <v>100</v>
@@ -3022,22 +3095,22 @@
         <v>100</v>
       </c>
       <c r="O33" s="3">
+        <v>100</v>
+      </c>
+      <c r="P33" s="3">
         <v>300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
-        <v>100</v>
-      </c>
       <c r="R33" s="3">
+        <v>100</v>
+      </c>
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U33" s="3">
         <v>100</v>
@@ -3052,13 +3125,13 @@
         <v>100</v>
       </c>
       <c r="Y33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z33" s="3">
         <v>200</v>
       </c>
       <c r="AA33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB33" s="3">
         <v>100</v>
@@ -3076,10 +3149,13 @@
         <v>100</v>
       </c>
       <c r="AG33" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,8 +3249,11 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3182,22 +3261,22 @@
         <v>100</v>
       </c>
       <c r="E35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K35" s="3">
         <v>100</v>
@@ -3212,22 +3291,22 @@
         <v>100</v>
       </c>
       <c r="O35" s="3">
+        <v>100</v>
+      </c>
+      <c r="P35" s="3">
         <v>300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
-        <v>100</v>
-      </c>
       <c r="R35" s="3">
+        <v>100</v>
+      </c>
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3">
         <v>100</v>
@@ -3242,13 +3321,13 @@
         <v>100</v>
       </c>
       <c r="Y35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z35" s="3">
         <v>200</v>
       </c>
       <c r="AA35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB35" s="3">
         <v>100</v>
@@ -3266,110 +3345,116 @@
         <v>100</v>
       </c>
       <c r="AG35" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E38" s="2">
         <v>45260</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45169</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45077</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44985</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44895</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44804</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44712</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44620</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44530</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44439</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44347</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44255</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44165</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44074</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43982</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43890</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43799</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43708</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43616</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43524</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43434</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43343</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43251</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43159</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43069</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42978</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42886</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42794</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42704</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,8 +3524,9 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3447,19 +3534,19 @@
         <v>1900</v>
       </c>
       <c r="E41" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="F41" s="3">
         <v>1700</v>
       </c>
       <c r="G41" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="H41" s="3">
         <v>1600</v>
       </c>
       <c r="I41" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="J41" s="3">
         <v>1500</v>
@@ -3474,28 +3561,28 @@
         <v>1500</v>
       </c>
       <c r="N41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O41" s="3">
         <v>1400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1100</v>
-      </c>
-      <c r="U41" s="3">
-        <v>1000</v>
       </c>
       <c r="V41" s="3">
         <v>1000</v>
@@ -3504,37 +3591,40 @@
         <v>1000</v>
       </c>
       <c r="X41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y41" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>900</v>
       </c>
       <c r="Z41" s="3">
         <v>900</v>
       </c>
       <c r="AA41" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="AB41" s="3">
         <v>800</v>
       </c>
       <c r="AC41" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD41" s="3">
         <v>700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,8 +3718,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3676,10 +3769,10 @@
         <v>100</v>
       </c>
       <c r="R43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3">
         <v>100</v>
@@ -3723,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3785,11 +3881,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
@@ -3818,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3827,25 +3926,25 @@
         <v>300</v>
       </c>
       <c r="E45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F45" s="3">
         <v>400</v>
       </c>
       <c r="G45" s="3">
+        <v>400</v>
+      </c>
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>700</v>
       </c>
       <c r="L45" s="3">
         <v>700</v>
@@ -3854,7 +3953,7 @@
         <v>700</v>
       </c>
       <c r="N45" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="O45" s="3">
         <v>500</v>
@@ -3863,13 +3962,13 @@
         <v>500</v>
       </c>
       <c r="Q45" s="3">
+        <v>500</v>
+      </c>
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>500</v>
       </c>
       <c r="T45" s="3">
         <v>500</v>
@@ -3887,13 +3986,13 @@
         <v>500</v>
       </c>
       <c r="Y45" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="Z45" s="3">
         <v>700</v>
       </c>
       <c r="AA45" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AB45" s="3">
         <v>800</v>
@@ -3902,7 +4001,7 @@
         <v>800</v>
       </c>
       <c r="AD45" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AE45" s="3">
         <v>700</v>
@@ -3913,8 +4012,11 @@
       <c r="AG45" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3922,7 +4024,7 @@
         <v>2300</v>
       </c>
       <c r="E46" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="F46" s="3">
         <v>2200</v>
@@ -3934,82 +4036,85 @@
         <v>2200</v>
       </c>
       <c r="I46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J46" s="3">
         <v>2600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2400</v>
-      </c>
-      <c r="K46" s="3">
-        <v>2300</v>
       </c>
       <c r="L46" s="3">
         <v>2300</v>
       </c>
       <c r="M46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N46" s="3">
         <v>2200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1700</v>
-      </c>
-      <c r="U46" s="3">
-        <v>1600</v>
       </c>
       <c r="V46" s="3">
         <v>1600</v>
       </c>
       <c r="W46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="X46" s="3">
         <v>1500</v>
-      </c>
-      <c r="X46" s="3">
-        <v>1700</v>
       </c>
       <c r="Y46" s="3">
         <v>1700</v>
       </c>
       <c r="Z46" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="AA46" s="3">
         <v>1600</v>
       </c>
       <c r="AB46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AC46" s="3">
         <v>1700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1600</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>1500</v>
       </c>
       <c r="AE46" s="3">
         <v>1500</v>
       </c>
       <c r="AF46" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG46" s="3">
         <v>1700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4031,8 +4136,8 @@
       <c r="I47" s="3">
         <v>0</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
+      <c r="J47" s="3">
+        <v>0</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
@@ -4049,8 +4154,8 @@
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4103,16 +4208,19 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3">
         <v>100</v>
@@ -4124,7 +4232,7 @@
         <v>100</v>
       </c>
       <c r="I48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>200</v>
@@ -4139,7 +4247,7 @@
         <v>200</v>
       </c>
       <c r="N48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
@@ -4154,7 +4262,7 @@
         <v>300</v>
       </c>
       <c r="S48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T48" s="3">
         <v>400</v>
@@ -4166,13 +4274,13 @@
         <v>400</v>
       </c>
       <c r="W48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="X48" s="3">
         <v>500</v>
       </c>
       <c r="Y48" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -4198,8 +4306,11 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>2000</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,19 +4600,22 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>5</v>
@@ -4506,14 +4626,14 @@
       <c r="I52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
@@ -4524,11 +4644,11 @@
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R52" s="3">
         <v>200</v>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,13 +4796,16 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4300</v>
+        <v>4700</v>
       </c>
       <c r="E54" s="3">
         <v>4300</v>
@@ -4694,10 +4820,10 @@
         <v>4300</v>
       </c>
       <c r="I54" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J54" s="3">
         <v>4800</v>
-      </c>
-      <c r="J54" s="3">
-        <v>4500</v>
       </c>
       <c r="K54" s="3">
         <v>4500</v>
@@ -4706,28 +4832,28 @@
         <v>4500</v>
       </c>
       <c r="M54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="N54" s="3">
         <v>4400</v>
-      </c>
-      <c r="N54" s="3">
-        <v>4200</v>
       </c>
       <c r="O54" s="3">
         <v>4200</v>
       </c>
       <c r="P54" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="Q54" s="3">
         <v>4100</v>
       </c>
       <c r="R54" s="3">
+        <v>4100</v>
+      </c>
+      <c r="S54" s="3">
         <v>3900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4000</v>
-      </c>
-      <c r="T54" s="3">
-        <v>4200</v>
       </c>
       <c r="U54" s="3">
         <v>4200</v>
@@ -4739,37 +4865,40 @@
         <v>4200</v>
       </c>
       <c r="X54" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Y54" s="3">
         <v>4400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3900</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>3800</v>
       </c>
       <c r="AA54" s="3">
         <v>3800</v>
       </c>
       <c r="AB54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AC54" s="3">
         <v>3900</v>
-      </c>
-      <c r="AC54" s="3">
-        <v>3800</v>
       </c>
       <c r="AD54" s="3">
         <v>3800</v>
       </c>
       <c r="AE54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AF54" s="3">
         <v>3700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4922,19 +5053,22 @@
         <v>0</v>
       </c>
       <c r="AD57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE57" s="3">
         <v>100</v>
       </c>
       <c r="AF57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4975,13 +5109,13 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>100</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
+        <v>200</v>
+      </c>
+      <c r="R58" s="3">
+        <v>100</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
@@ -4998,8 +5132,8 @@
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -5019,79 +5153,82 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>700</v>
+      </c>
+      <c r="E59" s="3">
         <v>600</v>
-      </c>
-      <c r="E59" s="3">
-        <v>800</v>
       </c>
       <c r="F59" s="3">
         <v>800</v>
       </c>
       <c r="G59" s="3">
+        <v>800</v>
+      </c>
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1100</v>
       </c>
       <c r="L59" s="3">
         <v>1100</v>
       </c>
       <c r="M59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N59" s="3">
         <v>1000</v>
-      </c>
-      <c r="N59" s="3">
-        <v>900</v>
       </c>
       <c r="O59" s="3">
         <v>900</v>
       </c>
       <c r="P59" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="Q59" s="3">
         <v>800</v>
       </c>
       <c r="R59" s="3">
+        <v>800</v>
+      </c>
+      <c r="S59" s="3">
         <v>700</v>
-      </c>
-      <c r="S59" s="3">
-        <v>900</v>
       </c>
       <c r="T59" s="3">
         <v>900</v>
       </c>
       <c r="U59" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="V59" s="3">
         <v>800</v>
       </c>
       <c r="W59" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="X59" s="3">
         <v>900</v>
@@ -5103,7 +5240,7 @@
         <v>900</v>
       </c>
       <c r="AA59" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB59" s="3">
         <v>1000</v>
@@ -5118,72 +5255,75 @@
         <v>1000</v>
       </c>
       <c r="AF59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG59" s="3">
         <v>1100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>800</v>
+      </c>
+      <c r="E60" s="3">
         <v>600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>900</v>
       </c>
       <c r="G60" s="3">
         <v>900</v>
       </c>
       <c r="H60" s="3">
+        <v>900</v>
+      </c>
+      <c r="I60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1200</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1100</v>
       </c>
       <c r="L60" s="3">
         <v>1100</v>
       </c>
       <c r="M60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N60" s="3">
         <v>1000</v>
-      </c>
-      <c r="N60" s="3">
-        <v>900</v>
       </c>
       <c r="O60" s="3">
         <v>900</v>
       </c>
       <c r="P60" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>700</v>
-      </c>
-      <c r="S60" s="3">
-        <v>900</v>
       </c>
       <c r="T60" s="3">
         <v>900</v>
       </c>
       <c r="U60" s="3">
+        <v>900</v>
+      </c>
+      <c r="V60" s="3">
         <v>800</v>
-      </c>
-      <c r="V60" s="3">
-        <v>900</v>
       </c>
       <c r="W60" s="3">
         <v>900</v>
@@ -5198,7 +5338,7 @@
         <v>900</v>
       </c>
       <c r="AA60" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB60" s="3">
         <v>1000</v>
@@ -5210,16 +5350,19 @@
         <v>1000</v>
       </c>
       <c r="AE60" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="AF60" s="3">
         <v>1100</v>
       </c>
       <c r="AG60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH60" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5263,13 +5406,13 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -5313,16 +5456,19 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800</v>
+      </c>
+      <c r="E62" s="3">
         <v>500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>400</v>
       </c>
       <c r="F62" s="3">
         <v>400</v>
@@ -5346,10 +5492,10 @@
         <v>400</v>
       </c>
       <c r="M62" s="3">
+        <v>400</v>
+      </c>
+      <c r="N62" s="3">
         <v>500</v>
-      </c>
-      <c r="N62" s="3">
-        <v>400</v>
       </c>
       <c r="O62" s="3">
         <v>400</v>
@@ -5370,7 +5516,7 @@
         <v>400</v>
       </c>
       <c r="U62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V62" s="3">
         <v>500</v>
@@ -5379,11 +5525,11 @@
         <v>500</v>
       </c>
       <c r="X62" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y62" s="3">
         <v>400</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5399,8 +5545,8 @@
       <c r="AD62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,55 +5848,58 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1200</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1300</v>
       </c>
       <c r="G66" s="3">
         <v>1300</v>
       </c>
       <c r="H66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I66" s="3">
         <v>1200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1700</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1600</v>
       </c>
       <c r="K66" s="3">
         <v>1600</v>
       </c>
       <c r="L66" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="M66" s="3">
         <v>1500</v>
       </c>
       <c r="N66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O66" s="3">
         <v>1400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1400</v>
-      </c>
-      <c r="R66" s="3">
-        <v>1300</v>
       </c>
       <c r="S66" s="3">
         <v>1300</v>
@@ -5753,7 +5911,7 @@
         <v>1300</v>
       </c>
       <c r="V66" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="W66" s="3">
         <v>1400</v>
@@ -5762,13 +5920,13 @@
         <v>1400</v>
       </c>
       <c r="Y66" s="3">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="Z66" s="3">
         <v>900</v>
       </c>
       <c r="AA66" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB66" s="3">
         <v>1000</v>
@@ -5780,16 +5938,19 @@
         <v>1000</v>
       </c>
       <c r="AE66" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="AF66" s="3">
         <v>1100</v>
       </c>
       <c r="AG66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH66" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,8 +6374,11 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6212,22 +6386,22 @@
         <v>-11100</v>
       </c>
       <c r="E72" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-11200</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-11300</v>
       </c>
       <c r="G72" s="3">
         <v>-11300</v>
       </c>
       <c r="H72" s="3">
-        <v>-11200</v>
+        <v>-11300</v>
       </c>
       <c r="I72" s="3">
         <v>-11200</v>
       </c>
       <c r="J72" s="3">
-        <v>-11300</v>
+        <v>-11200</v>
       </c>
       <c r="K72" s="3">
         <v>-11300</v>
@@ -6236,7 +6410,7 @@
         <v>-11300</v>
       </c>
       <c r="M72" s="3">
-        <v>-11400</v>
+        <v>-11300</v>
       </c>
       <c r="N72" s="3">
         <v>-11400</v>
@@ -6245,61 +6419,64 @@
         <v>-11400</v>
       </c>
       <c r="P72" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-11600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-11500</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-11300</v>
       </c>
       <c r="U72" s="3">
         <v>-11300</v>
       </c>
       <c r="V72" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="W72" s="3">
         <v>-11400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-11500</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-11300</v>
       </c>
       <c r="Y72" s="3">
         <v>-11300</v>
       </c>
       <c r="Z72" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-11400</v>
-      </c>
-      <c r="AC72" s="3">
-        <v>-11500</v>
       </c>
       <c r="AD72" s="3">
         <v>-11500</v>
       </c>
       <c r="AE72" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="AF72" s="3">
         <v>-11600</v>
-      </c>
-      <c r="AF72" s="3">
-        <v>-11500</v>
       </c>
       <c r="AG72" s="3">
         <v>-11500</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>-11500</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,31 +6766,34 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3100</v>
-      </c>
-      <c r="F76" s="3">
-        <v>3000</v>
       </c>
       <c r="G76" s="3">
         <v>3000</v>
       </c>
       <c r="H76" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I76" s="3">
         <v>3100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3000</v>
-      </c>
-      <c r="J76" s="3">
-        <v>2900</v>
       </c>
       <c r="K76" s="3">
         <v>2900</v>
@@ -6619,25 +6805,25 @@
         <v>2900</v>
       </c>
       <c r="N76" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="O76" s="3">
         <v>2800</v>
       </c>
       <c r="P76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Q76" s="3">
         <v>2600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2800</v>
-      </c>
-      <c r="T76" s="3">
-        <v>2900</v>
       </c>
       <c r="U76" s="3">
         <v>2900</v>
@@ -6646,40 +6832,43 @@
         <v>2900</v>
       </c>
       <c r="W76" s="3">
+        <v>2900</v>
+      </c>
+      <c r="X76" s="3">
         <v>2800</v>
-      </c>
-      <c r="X76" s="3">
-        <v>3000</v>
       </c>
       <c r="Y76" s="3">
         <v>3000</v>
       </c>
       <c r="Z76" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AA76" s="3">
         <v>2900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2800</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>2700</v>
       </c>
       <c r="AE76" s="3">
         <v>2700</v>
       </c>
       <c r="AF76" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="AG76" s="3">
         <v>2800</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,108 +6962,114 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E80" s="2">
         <v>45260</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45169</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45077</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44985</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44895</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44804</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44712</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44620</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44530</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44439</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44347</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44255</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44165</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44074</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43982</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43890</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43799</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43708</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43616</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43524</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43434</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43343</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43251</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43159</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43069</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42978</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42886</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42794</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42704</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6882,22 +7077,22 @@
         <v>100</v>
       </c>
       <c r="E81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K81" s="3">
         <v>100</v>
@@ -6912,22 +7107,22 @@
         <v>100</v>
       </c>
       <c r="O81" s="3">
+        <v>100</v>
+      </c>
+      <c r="P81" s="3">
         <v>300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
-        <v>100</v>
-      </c>
       <c r="R81" s="3">
+        <v>100</v>
+      </c>
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U81" s="3">
         <v>100</v>
@@ -6942,13 +7137,13 @@
         <v>100</v>
       </c>
       <c r="Y81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z81" s="3">
         <v>200</v>
       </c>
       <c r="AA81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB81" s="3">
         <v>100</v>
@@ -6966,10 +7161,13 @@
         <v>100</v>
       </c>
       <c r="AG81" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,32 +7787,35 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E89" s="3">
         <v>100</v>
       </c>
       <c r="F89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G89" s="3">
         <v>200</v>
       </c>
       <c r="H89" s="3">
+        <v>200</v>
+      </c>
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="J89" s="3">
-        <v>100</v>
-      </c>
       <c r="K89" s="3">
         <v>100</v>
       </c>
@@ -7606,31 +7823,31 @@
         <v>100</v>
       </c>
       <c r="M89" s="3">
+        <v>100</v>
+      </c>
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="N89" s="3">
-        <v>200</v>
-      </c>
       <c r="O89" s="3">
         <v>200</v>
       </c>
       <c r="P89" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q89" s="3">
         <v>300</v>
       </c>
-      <c r="Q89" s="3">
-        <v>100</v>
-      </c>
       <c r="R89" s="3">
+        <v>100</v>
+      </c>
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
-        <v>100</v>
-      </c>
       <c r="T89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V89" s="3">
         <v>100</v>
@@ -7639,37 +7856,40 @@
         <v>100</v>
       </c>
       <c r="X89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y89" s="3">
         <v>200</v>
       </c>
       <c r="Z89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC89" s="3">
         <v>100</v>
       </c>
       <c r="AD89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE89" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
-        <v>200</v>
-      </c>
       <c r="AG89" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7738,8 +7959,8 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>5</v>
@@ -7750,8 +7971,8 @@
       <c r="Q91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -7774,14 +7995,14 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7792,14 +8013,17 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
+      <c r="AF91" s="3">
+        <v>0</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,13 +8215,16 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -8083,8 +8313,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8160,19 +8394,19 @@
         <v>-100</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-200</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-100</v>
       </c>
       <c r="U96" s="3">
         <v>-100</v>
@@ -8181,10 +8415,10 @@
         <v>-100</v>
       </c>
       <c r="W96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X96" s="3">
         <v>-200</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-100</v>
       </c>
       <c r="Y96" s="3">
         <v>-100</v>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,8 +8741,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8540,19 +8786,19 @@
         <v>-100</v>
       </c>
       <c r="P100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>200</v>
+      </c>
+      <c r="T100" s="3">
         <v>-200</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-100</v>
       </c>
       <c r="U100" s="3">
         <v>-100</v>
@@ -8561,10 +8807,10 @@
         <v>-100</v>
       </c>
       <c r="W100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X100" s="3">
         <v>-200</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-100</v>
       </c>
       <c r="Y100" s="3">
         <v>-100</v>
@@ -8593,8 +8839,11 @@
       <c r="AG100" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,8 +8937,11 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8700,62 +8952,62 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
-        <v>200</v>
-      </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L102" s="3">
         <v>100</v>
       </c>
       <c r="M102" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N102" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O102" s="3">
         <v>100</v>
       </c>
       <c r="P102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q102" s="3">
         <v>300</v>
       </c>
-      <c r="Q102" s="3">
-        <v>100</v>
-      </c>
       <c r="R102" s="3">
+        <v>100</v>
+      </c>
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
-        <v>100</v>
-      </c>
       <c r="U102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
-        <v>100</v>
-      </c>
       <c r="Y102" s="3">
         <v>100</v>
       </c>
@@ -8763,7 +9015,7 @@
         <v>100</v>
       </c>
       <c r="AA102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB102" s="3">
         <v>0</v>
@@ -8772,15 +9024,18 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
-        <v>100</v>
-      </c>
       <c r="AG102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BABB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABB_QTR_FIN.xlsx
@@ -656,185 +656,189 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E7" s="2">
         <v>45351</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45260</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45169</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45077</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44985</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44895</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44804</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44712</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44620</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44530</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44439</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44347</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44255</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44165</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44074</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43982</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43890</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43799</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43708</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43616</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43524</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43434</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43343</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43251</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43159</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43069</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42978</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42886</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42794</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42704</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>900</v>
       </c>
       <c r="G8" s="3">
         <v>900</v>
       </c>
       <c r="H8" s="3">
+        <v>900</v>
+      </c>
+      <c r="I8" s="3">
         <v>700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>700</v>
-      </c>
-      <c r="M8" s="3">
-        <v>800</v>
       </c>
       <c r="N8" s="3">
         <v>800</v>
       </c>
       <c r="O8" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="P8" s="3">
         <v>700</v>
@@ -843,16 +847,16 @@
         <v>700</v>
       </c>
       <c r="R8" s="3">
+        <v>700</v>
+      </c>
+      <c r="S8" s="3">
         <v>600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>700</v>
-      </c>
-      <c r="U8" s="3">
-        <v>800</v>
       </c>
       <c r="V8" s="3">
         <v>800</v>
@@ -861,10 +865,10 @@
         <v>800</v>
       </c>
       <c r="X8" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y8" s="3">
         <v>700</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>600</v>
       </c>
       <c r="Z8" s="3">
         <v>600</v>
@@ -873,10 +877,10 @@
         <v>600</v>
       </c>
       <c r="AB8" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC8" s="3">
         <v>500</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>600</v>
       </c>
       <c r="AD8" s="3">
         <v>600</v>
@@ -885,16 +889,19 @@
         <v>600</v>
       </c>
       <c r="AF8" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG8" s="3">
         <v>500</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>600</v>
       </c>
       <c r="AH8" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,25 +1338,28 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1363,11 +1383,11 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-200</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1383,8 +1403,8 @@
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,8 +1576,9 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1559,10 +1586,10 @@
         <v>700</v>
       </c>
       <c r="E17" s="3">
+        <v>700</v>
+      </c>
+      <c r="F17" s="3">
         <v>800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>700</v>
       </c>
       <c r="G17" s="3">
         <v>700</v>
@@ -1580,37 +1607,37 @@
         <v>700</v>
       </c>
       <c r="L17" s="3">
+        <v>700</v>
+      </c>
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>700</v>
-      </c>
-      <c r="N17" s="3">
-        <v>600</v>
       </c>
       <c r="O17" s="3">
         <v>600</v>
       </c>
       <c r="P17" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>700</v>
-      </c>
-      <c r="V17" s="3">
-        <v>600</v>
       </c>
       <c r="W17" s="3">
         <v>600</v>
@@ -1619,10 +1646,10 @@
         <v>600</v>
       </c>
       <c r="Y17" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z17" s="3">
         <v>500</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>400</v>
       </c>
       <c r="AA17" s="3">
         <v>400</v>
@@ -1637,27 +1664,30 @@
         <v>400</v>
       </c>
       <c r="AE17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF17" s="3">
         <v>500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F18" s="3">
         <v>200</v>
@@ -1666,16 +1696,16 @@
         <v>200</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L18" s="3">
         <v>100</v>
@@ -1684,70 +1714,73 @@
         <v>100</v>
       </c>
       <c r="N18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P18" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="3">
         <v>300</v>
       </c>
-      <c r="Q18" s="3">
-        <v>100</v>
-      </c>
       <c r="R18" s="3">
         <v>100</v>
       </c>
       <c r="S18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U18" s="3">
         <v>100</v>
       </c>
       <c r="V18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W18" s="3">
         <v>200</v>
       </c>
       <c r="X18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y18" s="3">
         <v>100</v>
       </c>
       <c r="Z18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA18" s="3">
         <v>200</v>
       </c>
       <c r="AB18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD18" s="3">
         <v>200</v>
       </c>
       <c r="AE18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF18" s="3">
         <v>100</v>
       </c>
       <c r="AG18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH18" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,22 +1815,23 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1880,16 +1914,19 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F21" s="3">
         <v>200</v>
@@ -1898,16 +1935,16 @@
         <v>200</v>
       </c>
       <c r="H21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J21" s="3">
         <v>200</v>
       </c>
       <c r="K21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L21" s="3">
         <v>100</v>
@@ -1916,34 +1953,34 @@
         <v>100</v>
       </c>
       <c r="N21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="3">
         <v>400</v>
       </c>
-      <c r="Q21" s="3">
-        <v>100</v>
-      </c>
       <c r="R21" s="3">
         <v>100</v>
       </c>
       <c r="S21" s="3">
+        <v>100</v>
+      </c>
+      <c r="T21" s="3">
         <v>-100</v>
       </c>
-      <c r="T21" s="3">
-        <v>100</v>
-      </c>
       <c r="U21" s="3">
         <v>100</v>
       </c>
       <c r="V21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X21" s="3">
         <v>100</v>
@@ -1952,13 +1989,13 @@
         <v>100</v>
       </c>
       <c r="Z21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA21" s="3">
         <v>200</v>
       </c>
       <c r="AB21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC21" s="3">
         <v>100</v>
@@ -1976,10 +2013,13 @@
         <v>100</v>
       </c>
       <c r="AH21" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2052,14 +2092,14 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2076,16 +2116,19 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F23" s="3">
         <v>200</v>
@@ -2094,16 +2137,16 @@
         <v>200</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I23" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
         <v>200</v>
       </c>
       <c r="K23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L23" s="3">
         <v>100</v>
@@ -2112,34 +2155,34 @@
         <v>100</v>
       </c>
       <c r="N23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P23" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3">
-        <v>100</v>
-      </c>
       <c r="R23" s="3">
         <v>100</v>
       </c>
       <c r="S23" s="3">
+        <v>100</v>
+      </c>
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
-        <v>100</v>
-      </c>
       <c r="U23" s="3">
         <v>100</v>
       </c>
       <c r="V23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X23" s="3">
         <v>100</v>
@@ -2148,13 +2191,13 @@
         <v>100</v>
       </c>
       <c r="Z23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA23" s="3">
         <v>200</v>
       </c>
       <c r="AB23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC23" s="3">
         <v>100</v>
@@ -2172,18 +2215,21 @@
         <v>100</v>
       </c>
       <c r="AH23" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
@@ -2192,16 +2238,16 @@
         <v>100</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2210,20 +2256,20 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -2243,11 +2289,11 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,8 +2419,11 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2382,22 +2434,22 @@
         <v>100</v>
       </c>
       <c r="F26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L26" s="3">
         <v>100</v>
@@ -2412,22 +2464,22 @@
         <v>100</v>
       </c>
       <c r="P26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="3">
         <v>300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
-        <v>100</v>
-      </c>
       <c r="S26" s="3">
+        <v>100</v>
+      </c>
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
         <v>100</v>
@@ -2439,16 +2491,16 @@
         <v>100</v>
       </c>
       <c r="Y26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z26" s="3">
         <v>300</v>
       </c>
-      <c r="Z26" s="3">
-        <v>200</v>
-      </c>
       <c r="AA26" s="3">
         <v>200</v>
       </c>
       <c r="AB26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC26" s="3">
         <v>100</v>
@@ -2466,10 +2518,13 @@
         <v>100</v>
       </c>
       <c r="AH26" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2480,22 +2535,22 @@
         <v>100</v>
       </c>
       <c r="F27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L27" s="3">
         <v>100</v>
@@ -2510,22 +2565,22 @@
         <v>100</v>
       </c>
       <c r="P27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q27" s="3">
         <v>300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
-        <v>100</v>
-      </c>
       <c r="S27" s="3">
+        <v>100</v>
+      </c>
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
         <v>100</v>
@@ -2537,16 +2592,16 @@
         <v>100</v>
       </c>
       <c r="Y27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z27" s="3">
         <v>300</v>
       </c>
-      <c r="Z27" s="3">
-        <v>200</v>
-      </c>
       <c r="AA27" s="3">
         <v>200</v>
       </c>
       <c r="AB27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC27" s="3">
         <v>100</v>
@@ -2564,10 +2619,13 @@
         <v>100</v>
       </c>
       <c r="AH27" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2714,8 +2775,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
@@ -2732,12 +2793,12 @@
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-200</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2753,8 +2814,8 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,23 +3025,26 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -3056,8 +3126,11 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3068,22 +3141,22 @@
         <v>100</v>
       </c>
       <c r="F33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L33" s="3">
         <v>100</v>
@@ -3098,22 +3171,22 @@
         <v>100</v>
       </c>
       <c r="P33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="3">
         <v>300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
-        <v>100</v>
-      </c>
       <c r="S33" s="3">
+        <v>100</v>
+      </c>
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V33" s="3">
         <v>100</v>
@@ -3128,13 +3201,13 @@
         <v>100</v>
       </c>
       <c r="Z33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA33" s="3">
         <v>200</v>
       </c>
       <c r="AB33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC33" s="3">
         <v>100</v>
@@ -3152,10 +3225,13 @@
         <v>100</v>
       </c>
       <c r="AH33" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,8 +3328,11 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3264,22 +3343,22 @@
         <v>100</v>
       </c>
       <c r="F35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L35" s="3">
         <v>100</v>
@@ -3294,22 +3373,22 @@
         <v>100</v>
       </c>
       <c r="P35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q35" s="3">
         <v>300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
-        <v>100</v>
-      </c>
       <c r="S35" s="3">
+        <v>100</v>
+      </c>
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3">
         <v>100</v>
@@ -3324,13 +3403,13 @@
         <v>100</v>
       </c>
       <c r="Z35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA35" s="3">
         <v>200</v>
       </c>
       <c r="AB35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC35" s="3">
         <v>100</v>
@@ -3348,113 +3427,119 @@
         <v>100</v>
       </c>
       <c r="AH35" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E38" s="2">
         <v>45351</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45260</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45169</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45077</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44985</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44895</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44804</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44712</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44620</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44530</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44439</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44347</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44255</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44165</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44074</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43982</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43890</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43799</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43708</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43616</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43524</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43434</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43343</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43251</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43159</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43069</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42978</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42886</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42794</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42704</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,8 +3611,9 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3537,19 +3624,19 @@
         <v>1900</v>
       </c>
       <c r="F41" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="G41" s="3">
         <v>1700</v>
       </c>
       <c r="H41" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="I41" s="3">
         <v>1600</v>
       </c>
       <c r="J41" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="K41" s="3">
         <v>1500</v>
@@ -3564,28 +3651,28 @@
         <v>1500</v>
       </c>
       <c r="O41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P41" s="3">
         <v>1400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1100</v>
-      </c>
-      <c r="V41" s="3">
-        <v>1000</v>
       </c>
       <c r="W41" s="3">
         <v>1000</v>
@@ -3594,37 +3681,40 @@
         <v>1000</v>
       </c>
       <c r="Y41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z41" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>900</v>
       </c>
       <c r="AA41" s="3">
         <v>900</v>
       </c>
       <c r="AB41" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="AC41" s="3">
         <v>800</v>
       </c>
       <c r="AD41" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE41" s="3">
         <v>700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3772,10 +3865,10 @@
         <v>100</v>
       </c>
       <c r="S43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3">
         <v>100</v>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3884,11 +3980,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3929,25 +4028,25 @@
         <v>300</v>
       </c>
       <c r="F45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
       </c>
       <c r="H45" s="3">
+        <v>400</v>
+      </c>
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>700</v>
       </c>
       <c r="M45" s="3">
         <v>700</v>
@@ -3956,7 +4055,7 @@
         <v>700</v>
       </c>
       <c r="O45" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="P45" s="3">
         <v>500</v>
@@ -3965,13 +4064,13 @@
         <v>500</v>
       </c>
       <c r="R45" s="3">
+        <v>500</v>
+      </c>
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
-      </c>
-      <c r="T45" s="3">
-        <v>500</v>
       </c>
       <c r="U45" s="3">
         <v>500</v>
@@ -3989,13 +4088,13 @@
         <v>500</v>
       </c>
       <c r="Z45" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AA45" s="3">
         <v>700</v>
       </c>
       <c r="AB45" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AC45" s="3">
         <v>800</v>
@@ -4004,7 +4103,7 @@
         <v>800</v>
       </c>
       <c r="AE45" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AF45" s="3">
         <v>700</v>
@@ -4015,19 +4114,22 @@
       <c r="AH45" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="E46" s="3">
         <v>2300</v>
       </c>
       <c r="F46" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="G46" s="3">
         <v>2200</v>
@@ -4039,82 +4141,85 @@
         <v>2200</v>
       </c>
       <c r="J46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K46" s="3">
         <v>2600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2400</v>
-      </c>
-      <c r="L46" s="3">
-        <v>2300</v>
       </c>
       <c r="M46" s="3">
         <v>2300</v>
       </c>
       <c r="N46" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O46" s="3">
         <v>2200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1700</v>
-      </c>
-      <c r="V46" s="3">
-        <v>1600</v>
       </c>
       <c r="W46" s="3">
         <v>1600</v>
       </c>
       <c r="X46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Y46" s="3">
         <v>1500</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>1700</v>
       </c>
       <c r="Z46" s="3">
         <v>1700</v>
       </c>
       <c r="AA46" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="AB46" s="3">
         <v>1600</v>
       </c>
       <c r="AC46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD46" s="3">
         <v>1700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1600</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>1500</v>
       </c>
       <c r="AF46" s="3">
         <v>1500</v>
       </c>
       <c r="AG46" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AH46" s="3">
         <v>1700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4139,8 +4244,8 @@
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
+      <c r="K47" s="3">
+        <v>0</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>5</v>
@@ -4157,8 +4262,8 @@
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4211,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4220,10 +4328,10 @@
         <v>400</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3">
         <v>100</v>
@@ -4235,7 +4343,7 @@
         <v>100</v>
       </c>
       <c r="J48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
@@ -4250,7 +4358,7 @@
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
@@ -4265,7 +4373,7 @@
         <v>300</v>
       </c>
       <c r="T48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U48" s="3">
         <v>400</v>
@@ -4277,13 +4385,13 @@
         <v>400</v>
       </c>
       <c r="X48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y48" s="3">
         <v>500</v>
       </c>
       <c r="Z48" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>2000</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4614,11 +4734,11 @@
       <c r="E52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>5</v>
@@ -4629,14 +4749,14 @@
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
@@ -4647,11 +4767,11 @@
       <c r="P52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S52" s="3">
         <v>200</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,16 +4922,19 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E54" s="3">
         <v>4700</v>
-      </c>
-      <c r="E54" s="3">
-        <v>4300</v>
       </c>
       <c r="F54" s="3">
         <v>4300</v>
@@ -4823,10 +4949,10 @@
         <v>4300</v>
       </c>
       <c r="J54" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K54" s="3">
         <v>4800</v>
-      </c>
-      <c r="K54" s="3">
-        <v>4500</v>
       </c>
       <c r="L54" s="3">
         <v>4500</v>
@@ -4835,28 +4961,28 @@
         <v>4500</v>
       </c>
       <c r="N54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="O54" s="3">
         <v>4400</v>
-      </c>
-      <c r="O54" s="3">
-        <v>4200</v>
       </c>
       <c r="P54" s="3">
         <v>4200</v>
       </c>
       <c r="Q54" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="R54" s="3">
         <v>4100</v>
       </c>
       <c r="S54" s="3">
+        <v>4100</v>
+      </c>
+      <c r="T54" s="3">
         <v>3900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4000</v>
-      </c>
-      <c r="U54" s="3">
-        <v>4200</v>
       </c>
       <c r="V54" s="3">
         <v>4200</v>
@@ -4868,37 +4994,40 @@
         <v>4200</v>
       </c>
       <c r="Y54" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Z54" s="3">
         <v>4400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3900</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>3800</v>
       </c>
       <c r="AB54" s="3">
         <v>3800</v>
       </c>
       <c r="AC54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AD54" s="3">
         <v>3900</v>
-      </c>
-      <c r="AD54" s="3">
-        <v>3800</v>
       </c>
       <c r="AE54" s="3">
         <v>3800</v>
       </c>
       <c r="AF54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AG54" s="3">
         <v>3700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5056,19 +5187,22 @@
         <v>0</v>
       </c>
       <c r="AE57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF57" s="3">
         <v>100</v>
       </c>
       <c r="AG57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5112,13 +5246,13 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>100</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
+        <v>200</v>
+      </c>
+      <c r="S58" s="3">
+        <v>100</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>5</v>
@@ -5135,8 +5269,8 @@
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -5156,17 +5290,20 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5174,64 +5311,64 @@
         <v>700</v>
       </c>
       <c r="E59" s="3">
+        <v>700</v>
+      </c>
+      <c r="F59" s="3">
         <v>600</v>
-      </c>
-      <c r="F59" s="3">
-        <v>800</v>
       </c>
       <c r="G59" s="3">
         <v>800</v>
       </c>
       <c r="H59" s="3">
+        <v>800</v>
+      </c>
+      <c r="I59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1100</v>
       </c>
       <c r="M59" s="3">
         <v>1100</v>
       </c>
       <c r="N59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O59" s="3">
         <v>1000</v>
-      </c>
-      <c r="O59" s="3">
-        <v>900</v>
       </c>
       <c r="P59" s="3">
         <v>900</v>
       </c>
       <c r="Q59" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="R59" s="3">
         <v>800</v>
       </c>
       <c r="S59" s="3">
+        <v>800</v>
+      </c>
+      <c r="T59" s="3">
         <v>700</v>
-      </c>
-      <c r="T59" s="3">
-        <v>900</v>
       </c>
       <c r="U59" s="3">
         <v>900</v>
       </c>
       <c r="V59" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="W59" s="3">
         <v>800</v>
       </c>
       <c r="X59" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="Y59" s="3">
         <v>900</v>
@@ -5243,7 +5380,7 @@
         <v>900</v>
       </c>
       <c r="AB59" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AC59" s="3">
         <v>1000</v>
@@ -5258,75 +5395,78 @@
         <v>1000</v>
       </c>
       <c r="AG59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH59" s="3">
         <v>1100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>700</v>
+      </c>
+      <c r="E60" s="3">
         <v>800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>800</v>
-      </c>
-      <c r="G60" s="3">
-        <v>900</v>
       </c>
       <c r="H60" s="3">
         <v>900</v>
       </c>
       <c r="I60" s="3">
+        <v>900</v>
+      </c>
+      <c r="J60" s="3">
         <v>800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1200</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1100</v>
       </c>
       <c r="M60" s="3">
         <v>1100</v>
       </c>
       <c r="N60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O60" s="3">
         <v>1000</v>
-      </c>
-      <c r="O60" s="3">
-        <v>900</v>
       </c>
       <c r="P60" s="3">
         <v>900</v>
       </c>
       <c r="Q60" s="3">
+        <v>900</v>
+      </c>
+      <c r="R60" s="3">
         <v>1100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>700</v>
-      </c>
-      <c r="T60" s="3">
-        <v>900</v>
       </c>
       <c r="U60" s="3">
         <v>900</v>
       </c>
       <c r="V60" s="3">
+        <v>900</v>
+      </c>
+      <c r="W60" s="3">
         <v>800</v>
-      </c>
-      <c r="W60" s="3">
-        <v>900</v>
       </c>
       <c r="X60" s="3">
         <v>900</v>
@@ -5341,7 +5481,7 @@
         <v>900</v>
       </c>
       <c r="AB60" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AC60" s="3">
         <v>1000</v>
@@ -5353,16 +5493,19 @@
         <v>1000</v>
       </c>
       <c r="AF60" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="AG60" s="3">
         <v>1100</v>
       </c>
       <c r="AH60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AI60" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5409,13 +5552,13 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5468,10 +5614,10 @@
         <v>800</v>
       </c>
       <c r="E62" s="3">
+        <v>800</v>
+      </c>
+      <c r="F62" s="3">
         <v>500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>400</v>
       </c>
       <c r="G62" s="3">
         <v>400</v>
@@ -5495,10 +5641,10 @@
         <v>400</v>
       </c>
       <c r="N62" s="3">
+        <v>400</v>
+      </c>
+      <c r="O62" s="3">
         <v>500</v>
-      </c>
-      <c r="O62" s="3">
-        <v>400</v>
       </c>
       <c r="P62" s="3">
         <v>400</v>
@@ -5519,7 +5665,7 @@
         <v>400</v>
       </c>
       <c r="V62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W62" s="3">
         <v>500</v>
@@ -5528,11 +5674,11 @@
         <v>500</v>
       </c>
       <c r="Y62" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z62" s="3">
         <v>400</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5548,8 +5694,8 @@
       <c r="AE62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF62" s="3">
-        <v>0</v>
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,58 +6006,61 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1200</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1300</v>
       </c>
       <c r="H66" s="3">
         <v>1300</v>
       </c>
       <c r="I66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J66" s="3">
         <v>1200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1700</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1600</v>
       </c>
       <c r="L66" s="3">
         <v>1600</v>
       </c>
       <c r="M66" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="N66" s="3">
         <v>1500</v>
       </c>
       <c r="O66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P66" s="3">
         <v>1400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1400</v>
-      </c>
-      <c r="S66" s="3">
-        <v>1300</v>
       </c>
       <c r="T66" s="3">
         <v>1300</v>
@@ -5914,7 +6072,7 @@
         <v>1300</v>
       </c>
       <c r="W66" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="X66" s="3">
         <v>1400</v>
@@ -5923,13 +6081,13 @@
         <v>1400</v>
       </c>
       <c r="Z66" s="3">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="AA66" s="3">
         <v>900</v>
       </c>
       <c r="AB66" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AC66" s="3">
         <v>1000</v>
@@ -5941,16 +6099,19 @@
         <v>1000</v>
       </c>
       <c r="AF66" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="AG66" s="3">
         <v>1100</v>
       </c>
       <c r="AH66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AI66" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,8 +6548,11 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6389,22 +6563,22 @@
         <v>-11100</v>
       </c>
       <c r="F72" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="G72" s="3">
         <v>-11200</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-11300</v>
       </c>
       <c r="H72" s="3">
         <v>-11300</v>
       </c>
       <c r="I72" s="3">
-        <v>-11200</v>
+        <v>-11300</v>
       </c>
       <c r="J72" s="3">
         <v>-11200</v>
       </c>
       <c r="K72" s="3">
-        <v>-11300</v>
+        <v>-11200</v>
       </c>
       <c r="L72" s="3">
         <v>-11300</v>
@@ -6413,7 +6587,7 @@
         <v>-11300</v>
       </c>
       <c r="N72" s="3">
-        <v>-11400</v>
+        <v>-11300</v>
       </c>
       <c r="O72" s="3">
         <v>-11400</v>
@@ -6422,61 +6596,64 @@
         <v>-11400</v>
       </c>
       <c r="Q72" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="R72" s="3">
         <v>-11700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-11700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-11500</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-11300</v>
       </c>
       <c r="V72" s="3">
         <v>-11300</v>
       </c>
       <c r="W72" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="X72" s="3">
         <v>-11400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-11500</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>-11300</v>
       </c>
       <c r="Z72" s="3">
         <v>-11300</v>
       </c>
       <c r="AA72" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="AB72" s="3">
         <v>-11400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11400</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>-11500</v>
       </c>
       <c r="AE72" s="3">
         <v>-11500</v>
       </c>
       <c r="AF72" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="AG72" s="3">
         <v>-11600</v>
-      </c>
-      <c r="AG72" s="3">
-        <v>-11500</v>
       </c>
       <c r="AH72" s="3">
         <v>-11500</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>-11500</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,34 +6952,37 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>3000</v>
       </c>
       <c r="H76" s="3">
         <v>3000</v>
       </c>
       <c r="I76" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J76" s="3">
         <v>3100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3000</v>
-      </c>
-      <c r="K76" s="3">
-        <v>2900</v>
       </c>
       <c r="L76" s="3">
         <v>2900</v>
@@ -6808,25 +6994,25 @@
         <v>2900</v>
       </c>
       <c r="O76" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="P76" s="3">
         <v>2800</v>
       </c>
       <c r="Q76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="R76" s="3">
         <v>2600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2800</v>
-      </c>
-      <c r="U76" s="3">
-        <v>2900</v>
       </c>
       <c r="V76" s="3">
         <v>2900</v>
@@ -6835,40 +7021,43 @@
         <v>2900</v>
       </c>
       <c r="X76" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Y76" s="3">
         <v>2800</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>3000</v>
       </c>
       <c r="Z76" s="3">
         <v>3000</v>
       </c>
       <c r="AA76" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AB76" s="3">
         <v>2900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2800</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>2700</v>
       </c>
       <c r="AF76" s="3">
         <v>2700</v>
       </c>
       <c r="AG76" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="AH76" s="3">
         <v>2800</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,111 +7154,117 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E80" s="2">
         <v>45351</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45260</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45169</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45077</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44985</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44895</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44804</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44712</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44620</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44530</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44439</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44347</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44255</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44165</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44074</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43982</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43890</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43799</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43708</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43616</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43524</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43434</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43343</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43251</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43159</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43069</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42978</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42886</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42794</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42704</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7080,22 +7275,22 @@
         <v>100</v>
       </c>
       <c r="F81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L81" s="3">
         <v>100</v>
@@ -7110,22 +7305,22 @@
         <v>100</v>
       </c>
       <c r="P81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q81" s="3">
         <v>300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
-        <v>100</v>
-      </c>
       <c r="S81" s="3">
+        <v>100</v>
+      </c>
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V81" s="3">
         <v>100</v>
@@ -7140,13 +7335,13 @@
         <v>100</v>
       </c>
       <c r="Z81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA81" s="3">
         <v>200</v>
       </c>
       <c r="AB81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC81" s="3">
         <v>100</v>
@@ -7164,10 +7359,13 @@
         <v>100</v>
       </c>
       <c r="AH81" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI81" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,35 +8004,38 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F89" s="3">
         <v>100</v>
       </c>
       <c r="G89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H89" s="3">
         <v>200</v>
       </c>
       <c r="I89" s="3">
+        <v>200</v>
+      </c>
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>300</v>
       </c>
-      <c r="K89" s="3">
-        <v>100</v>
-      </c>
       <c r="L89" s="3">
         <v>100</v>
       </c>
@@ -7826,31 +8043,31 @@
         <v>100</v>
       </c>
       <c r="N89" s="3">
+        <v>100</v>
+      </c>
+      <c r="O89" s="3">
         <v>300</v>
       </c>
-      <c r="O89" s="3">
-        <v>200</v>
-      </c>
       <c r="P89" s="3">
         <v>200</v>
       </c>
       <c r="Q89" s="3">
+        <v>200</v>
+      </c>
+      <c r="R89" s="3">
         <v>300</v>
       </c>
-      <c r="R89" s="3">
-        <v>100</v>
-      </c>
       <c r="S89" s="3">
+        <v>100</v>
+      </c>
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
-        <v>100</v>
-      </c>
       <c r="U89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W89" s="3">
         <v>100</v>
@@ -7859,37 +8076,40 @@
         <v>100</v>
       </c>
       <c r="Y89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z89" s="3">
         <v>200</v>
       </c>
       <c r="AA89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD89" s="3">
         <v>100</v>
       </c>
       <c r="AE89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF89" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AG89" s="3">
-        <v>200</v>
-      </c>
       <c r="AH89" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AI89" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7962,8 +8183,8 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>5</v>
@@ -7974,8 +8195,8 @@
       <c r="R91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -7998,14 +8219,14 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -8016,14 +8237,17 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
+      <c r="AG91" s="3">
+        <v>0</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,16 +8445,19 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8397,19 +8631,19 @@
         <v>-100</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-200</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-100</v>
       </c>
       <c r="V96" s="3">
         <v>-100</v>
@@ -8418,10 +8652,10 @@
         <v>-100</v>
       </c>
       <c r="X96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-100</v>
       </c>
       <c r="Z96" s="3">
         <v>-100</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8789,19 +9035,19 @@
         <v>-100</v>
       </c>
       <c r="Q100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>200</v>
+      </c>
+      <c r="U100" s="3">
         <v>-200</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-100</v>
       </c>
       <c r="V100" s="3">
         <v>-100</v>
@@ -8810,10 +9056,10 @@
         <v>-100</v>
       </c>
       <c r="X100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-100</v>
       </c>
       <c r="Z100" s="3">
         <v>-100</v>
@@ -8842,8 +9088,11 @@
       <c r="AH100" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,8 +9189,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8955,62 +9207,62 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
-        <v>200</v>
-      </c>
       <c r="K102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M102" s="3">
         <v>100</v>
       </c>
       <c r="N102" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O102" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P102" s="3">
         <v>100</v>
       </c>
       <c r="Q102" s="3">
+        <v>100</v>
+      </c>
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
-        <v>100</v>
-      </c>
       <c r="S102" s="3">
+        <v>100</v>
+      </c>
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
-        <v>100</v>
-      </c>
       <c r="V102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
-        <v>100</v>
-      </c>
       <c r="Z102" s="3">
         <v>100</v>
       </c>
@@ -9018,7 +9270,7 @@
         <v>100</v>
       </c>
       <c r="AB102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC102" s="3">
         <v>0</v>
@@ -9027,15 +9279,18 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-200</v>
       </c>
-      <c r="AG102" s="3">
-        <v>100</v>
-      </c>
       <c r="AH102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI102" s="3">
         <v>100</v>
       </c>
     </row>
